--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1042,6 +1042,434 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123933514</v>
+      </c>
+      <c r="B5" t="n">
+        <v>39935</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101166</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre träfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Acossus terebra</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Luresten, Luresten, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566627</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6310477</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123933649</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4772</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Luresten, Luresten, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566570</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6310465</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123933581</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57507</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Luresten, Luresten, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566593</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6310486</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123933296</v>
+      </c>
+      <c r="B8" t="n">
+        <v>5361</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101728</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grön aspvedbock</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Saperda perforata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Luresten, Luresten, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566611</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6310466</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bäckebo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933514</v>
+        <v>123933581</v>
       </c>
       <c r="B5" t="n">
-        <v>39935</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,21 +1060,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101166</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566627</v>
+        <v>566593</v>
       </c>
       <c r="R5" t="n">
-        <v>6310477</v>
+        <v>6310486</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123933649</v>
+        <v>123933514</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>39935</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,25 +1163,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>101166</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566570</v>
+        <v>566627</v>
       </c>
       <c r="R6" t="n">
-        <v>6310465</v>
+        <v>6310477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933581</v>
+        <v>123933296</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>5361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566593</v>
+        <v>566611</v>
       </c>
       <c r="R7" t="n">
-        <v>6310486</v>
+        <v>6310466</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123933296</v>
+        <v>123933649</v>
       </c>
       <c r="B8" t="n">
-        <v>5361</v>
+        <v>4772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101728</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566611</v>
+        <v>566570</v>
       </c>
       <c r="R8" t="n">
-        <v>6310466</v>
+        <v>6310465</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933581</v>
+        <v>123933649</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566593</v>
+        <v>566570</v>
       </c>
       <c r="R5" t="n">
-        <v>6310486</v>
+        <v>6310465</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123933514</v>
+        <v>123933581</v>
       </c>
       <c r="B6" t="n">
-        <v>39935</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101166</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566627</v>
+        <v>566593</v>
       </c>
       <c r="R6" t="n">
-        <v>6310477</v>
+        <v>6310486</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123933649</v>
+        <v>123933514</v>
       </c>
       <c r="B8" t="n">
-        <v>4772</v>
+        <v>39935</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>101166</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566570</v>
+        <v>566627</v>
       </c>
       <c r="R8" t="n">
-        <v>6310465</v>
+        <v>6310477</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933649</v>
+        <v>123933514</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>39935</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>101166</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566570</v>
+        <v>566627</v>
       </c>
       <c r="R5" t="n">
-        <v>6310465</v>
+        <v>6310477</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123933514</v>
+        <v>123933649</v>
       </c>
       <c r="B8" t="n">
-        <v>39935</v>
+        <v>4772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,25 +1377,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101166</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566627</v>
+        <v>566570</v>
       </c>
       <c r="R8" t="n">
-        <v>6310477</v>
+        <v>6310465</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933514</v>
+        <v>123933649</v>
       </c>
       <c r="B5" t="n">
-        <v>39935</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101166</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566627</v>
+        <v>566570</v>
       </c>
       <c r="R5" t="n">
-        <v>6310477</v>
+        <v>6310465</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933649</v>
+        <v>123933514</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>39935</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,25 +1270,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>101166</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566570</v>
+        <v>566627</v>
       </c>
       <c r="R7" t="n">
-        <v>6310465</v>
+        <v>6310477</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123933581</v>
+        <v>123933514</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>39935</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>101166</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566593</v>
+        <v>566627</v>
       </c>
       <c r="R6" t="n">
-        <v>6310486</v>
+        <v>6310477</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933514</v>
+        <v>123933296</v>
       </c>
       <c r="B7" t="n">
-        <v>39935</v>
+        <v>5361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101166</v>
+        <v>101728</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566627</v>
+        <v>566611</v>
       </c>
       <c r="R7" t="n">
-        <v>6310477</v>
+        <v>6310466</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123933296</v>
+        <v>123933581</v>
       </c>
       <c r="B8" t="n">
-        <v>5361</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101728</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566611</v>
+        <v>566593</v>
       </c>
       <c r="R8" t="n">
-        <v>6310466</v>
+        <v>6310486</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933649</v>
+        <v>123933581</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566570</v>
+        <v>566593</v>
       </c>
       <c r="R5" t="n">
-        <v>6310465</v>
+        <v>6310486</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933296</v>
+        <v>123933649</v>
       </c>
       <c r="B7" t="n">
-        <v>5361</v>
+        <v>4772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,25 +1270,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101728</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566611</v>
+        <v>566570</v>
       </c>
       <c r="R7" t="n">
-        <v>6310466</v>
+        <v>6310465</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123933581</v>
+        <v>123933296</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>5361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>101728</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566593</v>
+        <v>566611</v>
       </c>
       <c r="R8" t="n">
-        <v>6310486</v>
+        <v>6310466</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 12441-2025 artfynd.xlsx
+++ b/artfynd/A 12441-2025 artfynd.xlsx
@@ -1044,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123933581</v>
+        <v>123933649</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>4772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566593</v>
+        <v>566570</v>
       </c>
       <c r="R5" t="n">
-        <v>6310486</v>
+        <v>6310465</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosökshack</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123933514</v>
+        <v>123933581</v>
       </c>
       <c r="B6" t="n">
-        <v>39935</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1167,21 +1167,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101166</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre träfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Acossus terebra</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1191,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566627</v>
+        <v>566593</v>
       </c>
       <c r="R6" t="n">
-        <v>6310477</v>
+        <v>6310486</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123933649</v>
+        <v>123933296</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>5361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,25 +1270,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>101728</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grön aspvedbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Saperda perforata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Pallas, 1773)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566570</v>
+        <v>566611</v>
       </c>
       <c r="R7" t="n">
-        <v>6310465</v>
+        <v>6310466</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123933296</v>
+        <v>123933514</v>
       </c>
       <c r="B8" t="n">
-        <v>5361</v>
+        <v>39935</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101728</v>
+        <v>101166</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön aspvedbock</t>
+          <t>Mindre träfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saperda perforata</t>
+          <t>Acossus terebra</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1773)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566611</v>
+        <v>566627</v>
       </c>
       <c r="R8" t="n">
-        <v>6310466</v>
+        <v>6310477</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>Kläckhål cirka 5 meter upp i nyligen död asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
